--- a/jpcore-r4/feature/値1つのみのValueSetを廃止する/StructureDefinition-jp-observation-dentaloral-toothtreatmentcondition.xlsx
+++ b/jpcore-r4/feature/値1つのみのValueSetを廃止する/StructureDefinition-jp-observation-dentaloral-toothtreatmentcondition.xlsx
@@ -907,7 +907,7 @@
     <t>second</t>
   </si>
   <si>
-    <t>このObservationに関するLOINC上の分類、必須項目</t>
+    <t>第2カテゴリはLOINCのコードLP89803-8固定とする、ValueSetのバインディングを指定していないことに注意すること</t>
   </si>
   <si>
     <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
